--- a/finance/基金交易记录与仓位分析.xlsx
+++ b/finance/基金交易记录与仓位分析.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05-Personal Project\finance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05-Personal Project\PersonalAbility\finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12540" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="基金信息" sheetId="4" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="161">
   <si>
     <t>基金信息与数据来源</t>
   </si>
@@ -485,6 +485,27 @@
   <si>
     <t>待确认，对2026/8/11买入的份额进行止盈，份额差额是下单的时候填错了</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>易方达机器人ETF联接C</t>
+  </si>
+  <si>
+    <t>机器人产业/具身智能/先进制造</t>
+  </si>
+  <si>
+    <t>国证机器人产业指数</t>
+  </si>
+  <si>
+    <t>机器人ETF易方达</t>
+  </si>
+  <si>
+    <t>0.159530</t>
+  </si>
+  <si>
+    <t>持有0-6日：1.50%；持有7日及以上：0</t>
+  </si>
+  <si>
+    <t>https://fund.eastmoney.com/020973.html</t>
   </si>
 </sst>
 </file>
@@ -497,7 +518,7 @@
     <numFmt numFmtId="178" formatCode="0.0000"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -564,8 +585,18 @@
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -602,8 +633,13 @@
         <fgColor rgb="FF2F75B5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="32">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -994,13 +1030,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1106,9 +1153,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1158,11 +1202,14 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1176,14 +1223,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="12" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="8" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1424,77 +1492,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="52" t="s">
+      <c r="H1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="53" t="s">
+      <c r="J1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="53" t="s">
+      <c r="K1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="53" t="s">
+      <c r="L1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="53" t="s">
+      <c r="M1" s="52" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="56"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="21"/>
@@ -1574,7 +1642,7 @@
       <c r="G6" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="49" t="s">
+      <c r="H6" s="48" t="s">
         <v>147</v>
       </c>
       <c r="I6" s="28">
@@ -1586,7 +1654,7 @@
       <c r="K6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="48" t="s">
+      <c r="L6" s="47" t="s">
         <v>21</v>
       </c>
       <c r="M6" s="28">
@@ -1615,7 +1683,7 @@
       <c r="G7" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="50" t="s">
+      <c r="H7" s="49" t="s">
         <v>148</v>
       </c>
       <c r="I7" s="28">
@@ -1627,7 +1695,7 @@
       <c r="K7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="48" t="s">
+      <c r="L7" s="47" t="s">
         <v>27</v>
       </c>
       <c r="M7" s="28">
@@ -1656,7 +1724,7 @@
       <c r="G8" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="50" t="s">
+      <c r="H8" s="49" t="s">
         <v>149</v>
       </c>
       <c r="I8" s="28">
@@ -1668,7 +1736,7 @@
       <c r="K8" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="48" t="s">
+      <c r="L8" s="47" t="s">
         <v>32</v>
       </c>
       <c r="M8" s="28">
@@ -1697,7 +1765,7 @@
       <c r="G9" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="50" t="s">
+      <c r="H9" s="49" t="s">
         <v>150</v>
       </c>
       <c r="I9" s="28">
@@ -1709,7 +1777,7 @@
       <c r="K9" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="48" t="s">
+      <c r="L9" s="47" t="s">
         <v>37</v>
       </c>
       <c r="M9" s="28">
@@ -1738,7 +1806,7 @@
       <c r="G10" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="H10" s="51" t="s">
+      <c r="H10" s="50" t="s">
         <v>151</v>
       </c>
       <c r="I10" s="28">
@@ -1750,15 +1818,53 @@
       <c r="K10" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="48" t="s">
+      <c r="L10" s="47" t="s">
         <v>43</v>
       </c>
       <c r="M10" s="28">
         <v>46251</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="H11" s="47"/>
+    <row r="11" spans="1:13" ht="42" customHeight="1">
+      <c r="A11" s="73">
+        <v>20973</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="74" t="s">
+        <v>156</v>
+      </c>
+      <c r="E11" s="75">
+        <v>159530</v>
+      </c>
+      <c r="F11" s="74" t="s">
+        <v>157</v>
+      </c>
+      <c r="G11" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="76" t="s">
+        <v>158</v>
+      </c>
+      <c r="I11" s="77">
+        <v>45433</v>
+      </c>
+      <c r="J11" s="78">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K11" s="74" t="s">
+        <v>159</v>
+      </c>
+      <c r="L11" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="M11" s="80">
+        <v>46251</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1800,125 +1906,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="58" t="s">
+      <c r="F1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="58" t="s">
+      <c r="G1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="58" t="s">
+      <c r="H1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="I1" s="58" t="s">
+      <c r="I1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="58" t="s">
+      <c r="J1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="58" t="s">
+      <c r="K1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="58" t="s">
+      <c r="L1" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="58" t="s">
+      <c r="M1" s="57" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="60" t="s">
+      <c r="G2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="60" t="s">
+      <c r="H2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="60" t="s">
+      <c r="K2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="L2" s="60" t="s">
+      <c r="L2" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="M2" s="61" t="s">
+      <c r="M2" s="60" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="63" t="s">
+      <c r="E3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="63" t="s">
+      <c r="G3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="63" t="s">
+      <c r="H3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="63" t="s">
+      <c r="I3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="J3" s="63" t="s">
+      <c r="J3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="K3" s="63" t="s">
+      <c r="K3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="L3" s="63" t="s">
+      <c r="L3" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="64" t="s">
+      <c r="M3" s="63" t="s">
         <v>45</v>
       </c>
     </row>
@@ -13149,16 +13255,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="21"/>
@@ -13171,28 +13277,28 @@
       <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="22.05" customHeight="1">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="73" t="s">
+      <c r="H3" s="66" t="s">
         <v>65</v>
       </c>
     </row>
@@ -13224,13 +13330,13 @@
       <c r="C5" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="72"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="65"/>
     </row>
     <row r="6" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A6" s="37" t="s">
@@ -13242,13 +13348,13 @@
       <c r="C6" s="38" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="71" t="s">
+      <c r="D6" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="72"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="65"/>
     </row>
     <row r="7" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A7" s="37" t="s">
@@ -13260,13 +13366,13 @@
       <c r="C7" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="D7" s="71" t="s">
+      <c r="D7" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="72"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A8" s="37" t="s">
@@ -13278,13 +13384,13 @@
       <c r="C8" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
-      <c r="G8" s="71"/>
-      <c r="H8" s="72"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="65"/>
     </row>
     <row r="9" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A9" s="37" t="s">
@@ -13296,13 +13402,13 @@
       <c r="C9" s="38" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="71" t="s">
+      <c r="D9" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="72"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="65"/>
     </row>
     <row r="10" spans="1:8" ht="37.950000000000003" customHeight="1">
       <c r="A10" s="37" t="s">
@@ -13314,13 +13420,13 @@
       <c r="C10" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="71" t="s">
+      <c r="D10" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="72"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="65"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="21"/>
@@ -13462,13 +13568,13 @@
       <c r="C19" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="D19" s="65" t="s">
+      <c r="D19" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="41"/>
@@ -13502,13 +13608,13 @@
       <c r="C22" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="D22" s="66" t="s">
+      <c r="D22" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
     </row>
     <row r="23" spans="1:8" ht="54" customHeight="1">
       <c r="A23" s="41" t="s">
@@ -13520,13 +13626,13 @@
       <c r="C23" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="65" t="s">
+      <c r="D23" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
     </row>
     <row r="24" spans="1:8" ht="54" customHeight="1">
       <c r="A24" s="41" t="s">
@@ -13538,13 +13644,13 @@
       <c r="C24" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="D24" s="65" t="s">
+      <c r="D24" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="E24" s="65"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
     </row>
     <row r="25" spans="1:8" ht="54" customHeight="1">
       <c r="A25" s="41" t="s">
@@ -13556,13 +13662,13 @@
       <c r="C25" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="D25" s="65" t="s">
+      <c r="D25" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="E25" s="65"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
     </row>
     <row r="26" spans="1:8" ht="54" customHeight="1">
       <c r="A26" s="41" t="s">
@@ -13574,13 +13680,13 @@
       <c r="C26" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="D26" s="65" t="s">
+      <c r="D26" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
     </row>
     <row r="27" spans="1:8" ht="54" customHeight="1">
       <c r="A27" s="41" t="s">
@@ -13592,13 +13698,13 @@
       <c r="C27" s="41" t="s">
         <v>141</v>
       </c>
-      <c r="D27" s="65" t="s">
+      <c r="D27" s="71" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="65"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
     </row>
     <row r="28" spans="1:8" ht="54" customHeight="1">
       <c r="A28" s="41" t="s">
@@ -13610,24 +13716,23 @@
       <c r="C28" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="65"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="71"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D28:H28"/>
+    <mergeCell ref="D22:H22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="D26:H26"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="D13:H13"/>
@@ -13637,13 +13742,14 @@
     <mergeCell ref="D17:H17"/>
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D27:H27"/>
-    <mergeCell ref="D28:H28"/>
-    <mergeCell ref="D22:H22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="D26:H26"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
